--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2021_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2021_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:46</t>
+    <t xml:space="preserve">2026-09-10 00:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2021_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2021_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:55</t>
+    <t xml:space="preserve">2026-09-18 11:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2021_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2021_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:04</t>
+    <t xml:space="preserve">2026-09-23 14:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2021_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2021_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 14:25</t>
+    <t xml:space="preserve">2026-10-02 16:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2021_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2021_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:06</t>
+    <t xml:space="preserve">2026-10-05 14:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -673,7 +673,7 @@
         <v>2021</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>5.62</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="9">
